--- a/02 Solution Architecture/AI/EPMP Gen AI use Cases.xlsx
+++ b/02 Solution Architecture/AI/EPMP Gen AI use Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/02 Solution Architecture/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A1D000-B83D-4D46-B49A-7BF1E4E25305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0F14EC-94B7-1C40-9D01-5805768460BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18100" xr2:uid="{20DAC78D-E20E-AE4C-BE55-673B816D1C62}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18100" activeTab="1" xr2:uid="{20DAC78D-E20E-AE4C-BE55-673B816D1C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Gen AI Use Cases" sheetId="1" r:id="rId1"/>
@@ -748,23 +748,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>469901</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>181498</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>97788</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>779133</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{788E15CA-5C7C-BCEC-356A-1C54EE07CBF0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0DD7995-3941-11CB-EBC0-0BA83FF7D570}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -780,8 +780,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="825500" y="609600"/>
-          <a:ext cx="11654788" cy="6375400"/>
+          <a:off x="469901" y="384698"/>
+          <a:ext cx="14342732" cy="7806802"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1367,7 +1367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="340" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="272" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="372" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="221" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="289" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="187" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="204" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="323" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="136" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="204" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="187" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="170" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="238" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="170" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="102" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>23</v>
       </c>
